--- a/tabtools/demo/demo_stacktab.xlsx
+++ b/tabtools/demo/demo_stacktab.xlsx
@@ -124,7 +124,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -134,17 +134,13 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <sz val="10"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
       <sz val="12"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Arial"/>
-      <b/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <b/>
       <name val="Arial"/>
     </font>
     <font>
@@ -156,6 +152,15 @@
       <sz val="10"/>
       <b/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="Arial"/>
+      <b/>
     </font>
     <font>
       <sz val="8"/>
@@ -175,7 +180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -184,6 +189,20 @@
       <diagonal/>
     </border>
     <border/>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
     <border>
       <left style="none"/>
       <right style="none"/>
@@ -194,8 +213,8 @@
     <border>
       <left style="none"/>
       <right style="none"/>
-      <top style="thin"/>
-      <bottom style="none"/>
+      <top style="none"/>
+      <bottom style="thin"/>
       <diagonal style="none"/>
     </border>
     <border>
@@ -208,122 +227,96 @@
     <border>
       <left style="none"/>
       <right style="none"/>
-      <top style="none"/>
-      <bottom style="thin"/>
+      <top style="thin"/>
+      <bottom style="none"/>
       <diagonal style="none"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -346,72 +339,72 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="4" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B5" s="14" t="s">
+      <c r="A5" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -434,58 +427,58 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="B1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12" t="s">
+      <c r="A2" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="A4" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="15" t="s">
+      <c r="C4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="5" t="s">
         <v>20</v>
       </c>
     </row>
@@ -506,73 +499,73 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
     </row>
     <row r="2">
-      <c r="B2" s="19" t="s">
+      <c r="B2" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="14" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="10" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="10" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="19" t="s">
+      <c r="B6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="19" t="s">
+      <c r="C6" s="14" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="18" t="s">
+      <c r="C8" s="13" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="true" ht="45" customHeight="true">
-      <c r="B9" s="28" t="s">
+      <c r="B9" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="28"/>
+      <c r="C9" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -594,53 +587,53 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
     </row>
     <row r="2">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="12" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="10" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="C4" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="18" t="s">
+      <c r="D4" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="E4" s="13" t="s">
         <v>28</v>
       </c>
     </row>

--- a/tabtools/demo/demo_stacktab.xlsx
+++ b/tabtools/demo/demo_stacktab.xlsx
@@ -180,7 +180,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -190,6 +190,27 @@
     </border>
     <border/>
     <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
@@ -198,7 +219,28 @@
     </border>
     <border>
       <left/>
+      <right style="thin"/>
+      <top/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
       <diagonal/>
@@ -235,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -244,79 +286,94 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="left" vertical="center" wrapText="true"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
       <alignment horizontal="left" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -339,16 +396,16 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -356,13 +413,13 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -370,13 +427,13 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>11</v>
       </c>
     </row>
@@ -384,13 +441,13 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
     </row>
@@ -398,13 +455,13 @@
       <c r="A5" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="8" t="s">
         <v>13</v>
       </c>
     </row>
@@ -427,16 +484,16 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="B1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
         <v>1</v>
       </c>
     </row>
@@ -444,13 +501,13 @@
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="10" t="s">
         <v>10</v>
       </c>
     </row>
@@ -458,13 +515,13 @@
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="6" t="s">
         <v>19</v>
       </c>
     </row>
@@ -472,13 +529,13 @@
       <c r="A4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="8" t="s">
         <v>20</v>
       </c>
     </row>
@@ -499,73 +556,73 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
     </row>
     <row r="2">
-      <c r="B2" s="14" t="s">
+      <c r="B2" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="15" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="15" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5">
-      <c r="B5" s="10" t="s">
+      <c r="B5" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="10" t="s">
+      <c r="C5" s="15" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="19" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="10" t="s">
+      <c r="B7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="18" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="9" s="1" customFormat="true" ht="45" customHeight="true">
-      <c r="B9" s="23" t="s">
+      <c r="B9" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="23"/>
+      <c r="C9" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -587,53 +644,53 @@
   </cols>
   <sheetData>
     <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
     </row>
     <row r="2">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="12" t="s">
+      <c r="C2" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="12" t="s">
+      <c r="D2" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="17" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="3">
-      <c r="B3" s="10" t="s">
+      <c r="B3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="15" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="4">
-      <c r="B4" s="13" t="s">
+      <c r="B4" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="13" t="s">
+      <c r="C4" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="13" t="s">
+      <c r="E4" s="18" t="s">
         <v>28</v>
       </c>
     </row>

--- a/tabtools/demo/demo_stacktab.xlsx
+++ b/tabtools/demo/demo_stacktab.xlsx
@@ -10,13 +10,14 @@
     <sheet name="Block Dose" sheetId="2" r:id="rId4"/>
     <sheet name="Composite" sheetId="3" r:id="rId5"/>
     <sheet name="SideBySide" sheetId="4" r:id="rId6"/>
+    <sheet name="Frames" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="125725" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="65" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="155" uniqueCount="76">
   <si>
     <t>Source block: Primary HRT exposure model</t>
   </si>
@@ -118,6 +119,132 @@
   </si>
   <si>
     <t>Table 2 supplement. Primary and dose-response estimates side by side</t>
+  </si>
+  <si>
+    <t>Table 1. Baseline Characteristics, All Patients and Aged 65+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Factor </t>
+  </si>
+  <si>
+    <t>All patients</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   No. (Column %) or Mean±SD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Age at cohort entry (years)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Female sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Education level</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Primary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Secondary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      Tertiary</t>
+  </si>
+  <si>
+    <t>Aged 65 and over</t>
+  </si>
+  <si>
+    <t>SSRI</t>
+  </si>
+  <si>
+    <t>N=8,929</t>
+  </si>
+  <si>
+    <t>55.9±13.4</t>
+  </si>
+  <si>
+    <t>5,530 (62)</t>
+  </si>
+  <si>
+    <t>2,280 (26)</t>
+  </si>
+  <si>
+    <t>3,524 (39)</t>
+  </si>
+  <si>
+    <t>3,125 (35)</t>
+  </si>
+  <si>
+    <t>N=2,473</t>
+  </si>
+  <si>
+    <t>72.1±4.7</t>
+  </si>
+  <si>
+    <t>1,539 (62)</t>
+  </si>
+  <si>
+    <t>634 (26)</t>
+  </si>
+  <si>
+    <t>980 (40)</t>
+  </si>
+  <si>
+    <t>859 (35)</t>
+  </si>
+  <si>
+    <t>SNRI</t>
+  </si>
+  <si>
+    <t>N=6,071</t>
+  </si>
+  <si>
+    <t>62.0±12.4</t>
+  </si>
+  <si>
+    <t>3,442 (57)</t>
+  </si>
+  <si>
+    <t>1,580 (26)</t>
+  </si>
+  <si>
+    <t>2,360 (39)</t>
+  </si>
+  <si>
+    <t>2,131 (35)</t>
+  </si>
+  <si>
+    <t>N=2,764</t>
+  </si>
+  <si>
+    <t>72.9±5.0</t>
+  </si>
+  <si>
+    <t>1,600 (58)</t>
+  </si>
+  <si>
+    <t>702 (25)</t>
+  </si>
+  <si>
+    <t>1,085 (39)</t>
+  </si>
+  <si>
+    <t>977 (35)</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>&lt;0.001</t>
+  </si>
+  <si>
+    <t>0.71</t>
+  </si>
+  <si>
+    <t>0.001</t>
+  </si>
+  <si>
+    <t>0.90</t>
   </si>
 </sst>
 </file>
@@ -180,7 +307,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="17">
     <border>
       <left/>
       <right/>
@@ -273,11 +400,32 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
@@ -376,6 +524,48 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -699,4 +889,331 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="1.7109375" style="1" customWidth="true"/>
+    <col min="2" max="2" width="31.7109375" style="1" customWidth="true"/>
+    <col min="3" max="3" width="12.7109375" style="1" customWidth="true"/>
+    <col min="4" max="4" width="12.7109375" style="1" customWidth="true"/>
+    <col min="5" max="5" width="9.7109375" style="1" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="true" ht="30" customHeight="true">
+      <c r="A1" s="42" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="42" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="D2" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="E2" s="40" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C4" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="E4" s="33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C5" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D6" s="32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C8" s="32" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="32" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C9" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" s="30" t="s">
+        <v>43</v>
+      </c>
+      <c r="C10" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D10" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="D11" s="37" t="s">
+        <v>1</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" s="30" t="s">
+        <v>37</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="D13" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" s="30" t="s">
+        <v>39</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" s="30" t="s">
+        <v>40</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C18" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="D18" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="35" t="s">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B11:E11"/>
+  </mergeCells>
+</worksheet>
 </file>
--- a/tabtools/demo/demo_stacktab.xlsx
+++ b/tabtools/demo/demo_stacktab.xlsx
@@ -1210,10 +1210,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B11:E11"/>
   </mergeCells>
 </worksheet>
 </file>